--- a/backend/data/DEPT - Master Data(Sheet1).xlsx
+++ b/backend/data/DEPT - Master Data(Sheet1).xlsx
@@ -300,7 +300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AB53"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="34.8" customHeight="1" s="5">
@@ -446,47 +446,45 @@
       </c>
     </row>
     <row r="2" ht="34.8" customHeight="1" s="5">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>D6203</t>
-        </is>
+      <c r="A2" s="6" t="n">
+        <v>44034</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>2000125883</v>
+        <v>1000044034</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
+          <t>DEEPAK  THAKUR</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>OFFSHORE</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>PUNE 3</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
           <t>MILIND  VIJAY MOKASHI</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>G8</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>OFFSHORE</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>PUNE 3</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>ABHISHEK  AWASTHI</t>
-        </is>
-      </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>10-Jun-24</t>
+          <t>18-Oct-18</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>24-Nov-25</t>
+          <t>7-Jul-25</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
@@ -495,17 +493,17 @@
         </is>
       </c>
       <c r="K2" s="7" t="n">
-        <v>2.04</v>
+        <v>7.69</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>2.04</v>
+        <v>21.19</v>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
@@ -515,52 +513,52 @@
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>milind.mokashi@deptagency.com</t>
+          <t>deepak.thakur@deptagency.com</t>
         </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S2" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T2" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>Managed Services, Scandlines, Inter Milan and Blackroll</t>
         </is>
       </c>
       <c r="U2" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>"Managed Services / Scandlines - Jasna Tanevska / Mandy Deegeling - Bleekman Inter Milan - Jack Darroch Blackroll - Sandor Voordes / Job Lampe"</t>
         </is>
       </c>
       <c r="V2" s="6" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="W2" s="6" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Mobile iOS developer</t>
         </is>
       </c>
       <c r="X2" s="6" t="inlineStr">
         <is>
-          <t>Hexa Sr</t>
+          <t>Premium Lead</t>
         </is>
       </c>
       <c r="Y2" s="6" t="inlineStr">
         <is>
-          <t>Non GCC</t>
+          <t>GCC</t>
         </is>
       </c>
       <c r="Z2" s="9" t="n"/>
@@ -572,20 +570,22 @@
       </c>
     </row>
     <row r="3" ht="158.4" customHeight="1" s="5">
-      <c r="A3" s="6" t="n">
-        <v>44034</v>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>G3788</t>
+        </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>1000044034</v>
+        <v>2000176154</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>DEEPAK  THAKUR</t>
+          <t>PRIYADARSH  TIWARI</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>18-Oct-18</t>
+          <t>28-Jan-26</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>7-Jul-25</t>
+          <t>3-Feb-26</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -619,17 +619,17 @@
         </is>
       </c>
       <c r="K3" s="7" t="n">
-        <v>7.69</v>
+        <v>0.41</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>21.19</v>
+        <v>4.91</v>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -639,47 +639,47 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>deepak.thakur@deptagency.com</t>
+          <t>priyadarsh.tiwari@deptagency.com</t>
         </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Managed Services, Scandlines, Inter Milan and Blackroll</t>
+          <t>Client TBD</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
         <is>
-          <t>"Managed Services / Scandlines - Jasna Tanevska / Mandy Deegeling - Bleekman Inter Milan - Jack Darroch Blackroll - Sandor Voordes / Job Lampe"</t>
+          <t>PM TBD</t>
         </is>
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>Mobile iOS developer</t>
+          <t>Salesforce CC B2C Developer</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>Premium Lead</t>
+          <t>Premium Mid</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
@@ -698,20 +698,20 @@
     <row r="4" ht="34.8" customHeight="1" s="5">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>G3788</t>
+          <t>G2788</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>2000176154</v>
+        <v>2000178660</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>PRIYADARSH  TIWARI</t>
+          <t>KULDEEP  MEHRA</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>28-Jan-26</t>
+          <t>5-Jan-26</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>3-Feb-26</t>
+          <t>10-Jan-26</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -745,17 +745,17 @@
         </is>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>4.91</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Drupal</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
@@ -765,22 +765,22 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>priyadarsh.tiwari@deptagency.com</t>
+          <t>kuldeep.mehra@deptagency.com</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T4" s="6" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Drupal</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>Salesforce CC B2C Developer</t>
+          <t>Drupal Developer</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>Premium Mid</t>
+          <t>Seniority TBD</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -813,31 +813,39 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z4" s="9" t="n"/>
-      <c r="AA4" s="9" t="n"/>
+      <c r="Z4" s="8" t="inlineStr">
+        <is>
+          <t>30-Apr-26</t>
+        </is>
+      </c>
+      <c r="AA4" s="6" t="inlineStr">
+        <is>
+          <t>Involuntary</t>
+        </is>
+      </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34.8" customHeight="1" s="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>G2788</t>
+          <t>G0941</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2000178660</v>
+        <v>2000175713</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>KULDEEP  MEHRA</t>
+          <t>AISHWARYA  PAWAR</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -857,12 +865,12 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>5-Jan-26</t>
+          <t>26-Nov-25</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>10-Jan-26</t>
+          <t>23-Dec-25</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -871,17 +879,17 @@
         </is>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>5.58</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>Drupal</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -891,47 +899,47 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>kuldeep.mehra@deptagency.com</t>
+          <t>aishwarya.pawar@deptagency.com</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Client TBD</t>
+          <t>ParsonKelloggs</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
         <is>
-          <t>PM TBD</t>
+          <t>Federico Flores , Keara Hanlon</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>Drupal</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>Drupal Developer</t>
+          <t>Salesforce Core Developer</t>
         </is>
       </c>
       <c r="X5" s="6" t="inlineStr">
         <is>
-          <t>Seniority TBD</t>
+          <t>Premium Mid</t>
         </is>
       </c>
       <c r="Y5" s="6" t="inlineStr">
@@ -939,39 +947,31 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z5" s="8" t="inlineStr">
-        <is>
-          <t>30-Apr-26</t>
-        </is>
-      </c>
-      <c r="AA5" s="6" t="inlineStr">
-        <is>
-          <t>Involuntary</t>
-        </is>
-      </c>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
       <c r="AB5" s="6" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.8" customHeight="1" s="5">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>G0941</t>
+          <t>G4124</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2000175713</v>
+        <v>2000183646</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>AISHWARYA  PAWAR</t>
+          <t>MANSI KAMLESH ATARA</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>26-Nov-25</t>
+          <t>3-Feb-26</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>23-Dec-25</t>
+          <t>6-Feb-26</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1005,17 +1005,17 @@
         </is>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.58</v>
+        <v>0.39</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>5.58</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>aishwarya.pawar@deptagency.com</t>
+          <t>mansi.atara@deptagency.com</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
@@ -1045,27 +1045,27 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>ParsonKelloggs</t>
+          <t>Barbour, PK Commerce</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
         <is>
-          <t>Federico Flores , Keara Hanlon</t>
+          <t>"Barbour - Sebastian Toledo farao PK Commerce - Keara hanlon"</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="W6" s="6" t="inlineStr">
         <is>
-          <t>Salesforce Core Developer</t>
+          <t>Manual QA Tester</t>
         </is>
       </c>
       <c r="X6" s="6" t="inlineStr">
         <is>
-          <t>Premium Mid</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y6" s="6" t="inlineStr">
@@ -1084,20 +1084,20 @@
     <row r="7" ht="68.5" customHeight="1" s="5">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>G4124</t>
+          <t>F8750</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2000183646</v>
+        <v>2000170189</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>MANSI KAMLESH ATARA</t>
+          <t>VIJAY  SWAMI</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>3-Feb-26</t>
+          <t>3-Oct-25</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>6-Feb-26</t>
+          <t>9-Oct-25</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -1131,17 +1131,17 @@
         </is>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>8.390000000000001</v>
+        <v>11.73</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>React JS</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>mansi.atara@deptagency.com</t>
+          <t>vijay.swami@deptagency.com</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTDE</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Barbour, PK Commerce</t>
+          <t>Lufthansa Digital Hangar</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
         <is>
-          <t>"Barbour - Sebastian Toledo farao PK Commerce - Keara hanlon"</t>
+          <t>Ajdien Taravati</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>Manual QA Tester</t>
+          <t>Front end developer - React Senior</t>
         </is>
       </c>
       <c r="X7" s="6" t="inlineStr">
@@ -1210,20 +1210,20 @@
     <row r="8" ht="34.8" customHeight="1" s="5">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>F8750</t>
+          <t>G6134</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>2000170189</v>
+        <v>2000179255</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>VIJAY  SWAMI</t>
+          <t>AKASH SHRAVAN  BARVE</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>MILIND  VIJAY MOKASHI</t>
+          <t>RUBAN JABA  SINGH J</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>3-Oct-25</t>
+          <t>19-Mar-26</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>9-Oct-25</t>
+          <t>26-Mar-26</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1257,17 +1257,17 @@
         </is>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.73</v>
+        <v>0.27</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>11.73</v>
+        <v>6.77</v>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>React JS</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
@@ -1277,47 +1277,47 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>vijay.swami@deptagency.com</t>
+          <t>akash.barve@deptagency.com</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>DTDE</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Lufthansa Digital Hangar</t>
+          <t>ParsonKelloggs, Barbour</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
         <is>
-          <t>Ajdien Taravati</t>
+          <t>"ParsonKelloggs - Steve Holsinger Barbour - Sebastian Toledo Farao"</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
-          <t>Front end developer - React Senior</t>
+          <t>Salesforce Core Developer</t>
         </is>
       </c>
       <c r="X8" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Premium Senior</t>
         </is>
       </c>
       <c r="Y8" s="6" t="inlineStr">
@@ -1336,20 +1336,20 @@
     <row r="9" ht="68.5" customHeight="1" s="5">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>G6134</t>
+          <t>C1790</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2000179255</v>
+        <v>2000103557</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>AKASH SHRAVAN  BARVE</t>
+          <t>SAUMYARANJAN  KANUNGO</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>RUBAN JABA  SINGH J</t>
+          <t>MILIND  VIJAY MOKASHI</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>19-Mar-26</t>
+          <t>23-Aug-23</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>26-Mar-26</t>
+          <t>1-Sep-25</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1383,17 +1383,17 @@
         </is>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.27</v>
+        <v>2.84</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>6.5</v>
+        <v>7.11</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>6.77</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
@@ -1403,47 +1403,47 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>akash.barve@deptagency.com</t>
+          <t>saumyaranjan.kanungo@deptagency.com</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>ParsonKelloggs, Barbour</t>
+          <t>Managed Services</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
-          <t>"ParsonKelloggs - Steve Holsinger Barbour - Sebastian Toledo Farao"</t>
+          <t>Mandy Deegeling</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>Salesforce Core Developer</t>
+          <t>Front end developer</t>
         </is>
       </c>
       <c r="X9" s="6" t="inlineStr">
         <is>
-          <t>Premium Senior</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y9" s="6" t="inlineStr">
@@ -1462,20 +1462,20 @@
     <row r="10" ht="34.8" customHeight="1" s="5">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>C1790</t>
+          <t>G3637</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>2000103557</v>
+        <v>2000178982</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>SAUMYARANJAN  KANUNGO</t>
+          <t>PRAMOD  KABUGADE</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>23-Aug-23</t>
+          <t>21-Jan-26</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>1-Sep-25</t>
+          <t>28-Jan-26</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -1509,17 +1509,17 @@
         </is>
       </c>
       <c r="K10" s="7" t="n">
-        <v>2.84</v>
+        <v>0.43</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>7.11</v>
+        <v>14</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>9.949999999999999</v>
+        <v>14.43</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>saumyaranjan.kanungo@deptagency.com</t>
+          <t>pramod.kabugade@deptagency.com</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>UKI</t>
         </is>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Managed Services</t>
+          <t>Audley Travel</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
-          <t>Mandy Deegeling</t>
+          <t>Dusica Djisalov</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
-          <t>Front end developer</t>
+          <t>Manual QA Tester</t>
         </is>
       </c>
       <c r="X10" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Standard Senior</t>
         </is>
       </c>
       <c r="Y10" s="6" t="inlineStr">
@@ -1588,20 +1588,20 @@
     <row r="11" ht="34.8" customHeight="1" s="5">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>G3637</t>
+          <t>C9326</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>2000178982</v>
+        <v>2000115259</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>PRAMOD  KABUGADE</t>
+          <t>SUDIPTO CHATTERJEE</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>21-Jan-26</t>
+          <t>14-Feb-24</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>28-Jan-26</t>
+          <t>6-Aug-25</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1635,17 +1635,17 @@
         </is>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.43</v>
+        <v>2.36</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>14</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>14.43</v>
+        <v>16.36</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>pramod.kabugade@deptagency.com</t>
+          <t>sudipto.chatterjee@deptagency.com</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -1675,32 +1675,32 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Audley Travel</t>
+          <t>Diageo</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
-          <t>Dusica Djisalov</t>
+          <t>Marie Moran</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>Manual QA Tester</t>
+          <t>Senior Front end developer</t>
         </is>
       </c>
       <c r="X11" s="6" t="inlineStr">
         <is>
-          <t>Standard Senior</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y11" s="6" t="inlineStr">
         <is>
-          <t>GCC</t>
+          <t>Non GCC</t>
         </is>
       </c>
       <c r="Z11" s="9" t="n"/>
@@ -1714,20 +1714,20 @@
     <row r="12" ht="34.8" customHeight="1" s="5">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>G5498</t>
+          <t>G0188</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>2000186338</v>
+        <v>2000173424</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>SAKSHI MADAN AGARWAL</t>
+          <t>RUPESH  KHARJUL</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>BHARATH  KANDASAMY</t>
+          <t>MILIND  VIJAY MOKASHI</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>5-Mar-26</t>
+          <t>8-Nov-25</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>5-Mar-26</t>
+          <t>14-Nov-25</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1761,17 +1761,17 @@
         </is>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.31</v>
+        <v>10.13</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
@@ -1781,47 +1781,47 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>sakshi.agarwal@deptagency.com</t>
+          <t>rupesh.kharjul@deptagency.com</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>Inter, Artis, Scandlines, Mauritshuis</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>Hexaware</t>
+          <t>"Inter - Nikola Petrovic Scandlines,Artis, Mauritshuis-Jasna Tanevska"</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>DGM - HR</t>
+          <t>Mobile Developer Android</t>
         </is>
       </c>
       <c r="X12" s="6" t="inlineStr">
         <is>
-          <t>Hexa Sr</t>
+          <t>Premium Senior</t>
         </is>
       </c>
       <c r="Y12" s="6" t="inlineStr">
@@ -1840,20 +1840,20 @@
     <row r="13" ht="34.8" customHeight="1" s="5">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>C9326</t>
+          <t>G4406</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>2000115259</v>
+        <v>2000181798</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>SUDIPTO CHATTERJEE</t>
+          <t>AJAYKUMAR BABURAO  KAYANDE</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>14-Feb-24</t>
+          <t>10-Feb-26</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>6-Aug-25</t>
+          <t>5-Mar-26</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1887,17 +1887,17 @@
         </is>
       </c>
       <c r="K13" s="7" t="n">
-        <v>2.36</v>
+        <v>0.37</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>16.36</v>
+        <v>7.87</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>sudipto.chatterjee@deptagency.com</t>
+          <t>ajaykumarkayane@deptagency.com</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -1922,37 +1922,37 @@
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>UKI</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>Diageo</t>
+          <t>Bol-Lowlands/Rockwerchter and Hubo</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>Marie Moran</t>
+          <t>"Lowlands/RockWerchter - Zowi Koster Hubo - Jasna Tanevska"</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>Senior Front end developer</t>
+          <t>Shopify Developer</t>
         </is>
       </c>
       <c r="X13" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Premium Senior</t>
         </is>
       </c>
       <c r="Y13" s="6" t="inlineStr">
         <is>
-          <t>Non GCC</t>
+          <t>GCC</t>
         </is>
       </c>
       <c r="Z13" s="9" t="n"/>
@@ -1966,20 +1966,20 @@
     <row r="14" ht="68.5" customHeight="1" s="5">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>G0188</t>
+          <t>G4271</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>2000173424</v>
+        <v>2000184187</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>RUPESH  KHARJUL</t>
+          <t>DUDDI  PRADEEP KUMAR</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>8-Nov-25</t>
+          <t>7-Feb-26</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>14-Nov-25</t>
+          <t>16-Feb-26</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -2013,17 +2013,17 @@
         </is>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.63</v>
+        <v>0.38</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>10.13</v>
+        <v>13.38</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Content Migration</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
@@ -2033,47 +2033,47 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>rupesh.kharjul@deptagency.com</t>
+          <t>duddi.kumar@deptagency .com</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>Inter, Artis, Scandlines, Mauritshuis</t>
+          <t>ParsonKelloggs, Arcadis</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>"Inter - Nikola Petrovic Scandlines,Artis, Mauritshuis-Jasna Tanevska"</t>
+          <t>"ParsonKelloggs - Kaera Hanlon Arcadis - Kristen Loch"</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Content Migration</t>
         </is>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>Mobile Developer Android</t>
+          <t>Content Migration Lead</t>
         </is>
       </c>
       <c r="X14" s="6" t="inlineStr">
         <is>
-          <t>Premium Senior</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y14" s="6" t="inlineStr">
@@ -2090,22 +2090,20 @@
       </c>
     </row>
     <row r="15" ht="57.3" customHeight="1" s="5">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>G4406</t>
-        </is>
+      <c r="A15" s="6" t="n">
+        <v>71544</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>2000181798</v>
+        <v>1000071544</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>AJAYKUMAR BABURAO  KAYANDE</t>
+          <t>SANIKA  ATHAVALE</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G3A</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -2120,17 +2118,17 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>MILIND  VIJAY MOKASHI</t>
+          <t>DUDDI  PRADEEP KUMAR</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>10-Feb-26</t>
+          <t>17-Mar-22</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>5-Mar-26</t>
+          <t>18-Feb-26</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -2139,17 +2137,17 @@
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.37</v>
+        <v>4.28</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>7.5</v>
+        <v>3.11</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>7.87</v>
+        <v>7.39</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Content Migration</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
@@ -2159,47 +2157,47 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>ajaykumarkayane@deptagency.com</t>
+          <t>sanika.athavale@deptagency.com</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>Bol-Lowlands/Rockwerchter and Hubo</t>
+          <t>Arcadis</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>"Lowlands/RockWerchter - Zowi Koster Hubo - Jasna Tanevska"</t>
+          <t>Kristen Loch</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Content Migration</t>
         </is>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>Shopify Developer</t>
+          <t>Junior Content Migration Specialist</t>
         </is>
       </c>
       <c r="X15" s="6" t="inlineStr">
         <is>
-          <t>Premium Senior</t>
+          <t>Standard Mid</t>
         </is>
       </c>
       <c r="Y15" s="6" t="inlineStr">
@@ -2218,15 +2216,15 @@
     <row r="16" ht="57.3" customHeight="1" s="5">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>G4271</t>
+          <t>G2619</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>2000184187</v>
+        <v>2000179645</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>DUDDI  PRADEEP KUMAR</t>
+          <t>NAVEEN KUMAR  MISHRA</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2251,12 +2249,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>7-Feb-26</t>
+          <t>29-Dec-25</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>16-Feb-26</t>
+          <t>9-Jan-26</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -2265,17 +2263,17 @@
         </is>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>13.38</v>
+        <v>11.49</v>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Content Migration</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
@@ -2285,47 +2283,47 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>duddi.kumar@deptagency .com</t>
+          <t>naveen.kumarmishra@deptagency.com</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>ParsonKelloggs, Arcadis</t>
+          <t>Blackroll</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
-          <t>"ParsonKelloggs - Kaera Hanlon Arcadis - Kristen Loch"</t>
+          <t>Job Lampe</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>Content Migration</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>Content Migration Lead</t>
+          <t>Mobile Developer Android</t>
         </is>
       </c>
       <c r="X16" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Premium Senior</t>
         </is>
       </c>
       <c r="Y16" s="6" t="inlineStr">
@@ -2342,20 +2340,22 @@
       </c>
     </row>
     <row r="17" ht="34.8" customHeight="1" s="5">
-      <c r="A17" s="6" t="n">
-        <v>71544</v>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>G1151</t>
+        </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>1000071544</v>
+        <v>2000176281</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>SANIKA  ATHAVALE</t>
+          <t>HARSH  KHARBANDA</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>G3A</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>DUDDI  PRADEEP KUMAR</t>
+          <t>MILIND  VIJAY MOKASHI</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>17-Mar-22</t>
+          <t>28-Nov-25</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>18-Feb-26</t>
+          <t>8-Dec-25</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2389,17 +2389,17 @@
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>4.28</v>
+        <v>0.58</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3.11</v>
+        <v>17</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>7.39</v>
+        <v>17.58</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>Content Migration</t>
+          <t>Drupal</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
@@ -2409,47 +2409,47 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>sanika.athavale@deptagency.com</t>
+          <t>harsh.kharbanda@deptagency.com</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>UKI</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>Arcadis</t>
+          <t>GNI, SEAI, SPOC, Calor Gas, Eirgrid</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
-          <t>Kristen Loch</t>
+          <t>"GNI - Kev Kellaghan SEAI &amp; SPOC - Kev Kellaghan, Jill Jordan CalorGas - Ashleigh Foy Eirgrid - Aine McNamara"</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>Content Migration</t>
+          <t>Drupal</t>
         </is>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>Junior Content Migration Specialist</t>
+          <t>Drupal Developer</t>
         </is>
       </c>
       <c r="X17" s="6" t="inlineStr">
         <is>
-          <t>Standard Mid</t>
+          <t>Premium Lead</t>
         </is>
       </c>
       <c r="Y17" s="6" t="inlineStr">
@@ -2468,20 +2468,20 @@
     <row r="18" ht="34.8" customHeight="1" s="5">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>G2619</t>
+          <t>G4075</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>2000179645</v>
+        <v>2000183604</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>NAVEEN KUMAR  MISHRA</t>
+          <t>AYUSH  PATIDAR</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>MILIND  VIJAY MOKASHI</t>
+          <t>ABHISHEK  AWASTHI</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>29-Dec-25</t>
+          <t>2-Feb-26</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>9-Jan-26</t>
+          <t>6-Feb-26</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -2515,17 +2515,17 @@
         </is>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>11.49</v>
+        <v>8.19</v>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>naveen.kumarmishra@deptagency.com</t>
+          <t>ayush.patidar@deptagency.com</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -2550,32 +2550,32 @@
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>UKI</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>Blackroll</t>
+          <t>Beautypie</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
         <is>
-          <t>Job Lampe</t>
+          <t>Manish Joshi</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Boomi</t>
         </is>
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
-          <t>Mobile Developer Android</t>
+          <t>Senior Dell Boomi Developer</t>
         </is>
       </c>
       <c r="X18" s="6" t="inlineStr">
         <is>
-          <t>Premium Senior</t>
+          <t>Premium Mid</t>
         </is>
       </c>
       <c r="Y18" s="6" t="inlineStr">
@@ -2594,20 +2594,20 @@
     <row r="19" ht="113.45" customHeight="1" s="5">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>G1151</t>
+          <t>D7254</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>2000176281</v>
+        <v>2000127864</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>HARSH  KHARBANDA</t>
+          <t>RAHUL MADHUSUDHAN  PATHAK</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>28-Nov-25</t>
+          <t>1-Jul-24</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>8-Dec-25</t>
+          <t>29-Jan-26</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -2641,17 +2641,17 @@
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.58</v>
+        <v>1.99</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>17</v>
+        <v>10.6</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>17.58</v>
+        <v>12.59</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>Drupal</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
@@ -2661,47 +2661,47 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>harsh.kharbanda@deptagency.com</t>
+          <t>rahul.pathak@deptagency.com</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>UKI</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>GNI, SEAI, SPOC, Calor Gas, Eirgrid</t>
+          <t>CFL</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
-          <t>"GNI - Kev Kellaghan SEAI &amp; SPOC - Kev Kellaghan, Jill Jordan CalorGas - Ashleigh Foy Eirgrid - Aine McNamara"</t>
+          <t>Daniel Schaerer</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>Drupal</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>Drupal Developer</t>
+          <t>Manual QA Tester</t>
         </is>
       </c>
       <c r="X19" s="6" t="inlineStr">
         <is>
-          <t>Premium Lead</t>
+          <t>Standard Senior</t>
         </is>
       </c>
       <c r="Y19" s="6" t="inlineStr">
@@ -2720,20 +2720,20 @@
     <row r="20" ht="34.8" customHeight="1" s="5">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>G4075</t>
+          <t>G3004</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>2000183604</v>
+        <v>2000178222</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>AYUSH  PATIDAR</t>
+          <t>SHANI RANJAN TIWARI</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>ABHISHEK  AWASTHI</t>
+          <t>MILIND  VIJAY MOKASHI</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>2-Feb-26</t>
+          <t>9-Jan-26</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>6-Feb-26</t>
+          <t>19-Jan-26</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -2767,17 +2767,17 @@
         </is>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>8.19</v>
+        <v>5.76</v>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
@@ -2787,47 +2787,47 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>ayush.patidar@deptagency.com</t>
+          <t>shani.tiwari@deptagency.com</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>UKI</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>Beautypie</t>
+          <t>Barbour</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>Manish Joshi</t>
+          <t>Sebastian Farao</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>Boomi</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="W20" s="6" t="inlineStr">
         <is>
-          <t>Senior Dell Boomi Developer</t>
+          <t>Salesforce CC B2C Developer</t>
         </is>
       </c>
       <c r="X20" s="6" t="inlineStr">
         <is>
-          <t>Premium Mid</t>
+          <t>Premium Senior</t>
         </is>
       </c>
       <c r="Y20" s="6" t="inlineStr">
@@ -2846,20 +2846,20 @@
     <row r="21" ht="46.05" customHeight="1" s="5">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>D7254</t>
+          <t>G4959</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>2000127864</v>
+        <v>2000185148</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>RAHUL MADHUSUDHAN  PATHAK</t>
+          <t>ROMIT  PANDITA</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>1-Jul-24</t>
+          <t>25-Feb-26</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>29-Jan-26</t>
+          <t>2-Mar-26</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -2893,17 +2893,17 @@
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>1.99</v>
+        <v>0.33</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>12.59</v>
+        <v>12.33</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Content Migration</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>rahul.pathak@deptagency.com</t>
+          <t>romit.pandita@deptagency.com</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>CFL</t>
+          <t>Arcadis</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
         <is>
-          <t>Daniel Schaerer</t>
+          <t>Kristen Loch</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Content Migration</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>Manual QA Tester</t>
+          <t>Senior Content Migration Specialist</t>
         </is>
       </c>
       <c r="X21" s="6" t="inlineStr">
@@ -2972,20 +2972,20 @@
     <row r="22" ht="34.8" customHeight="1" s="5">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>G3004</t>
+          <t>F9294</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>2000178222</v>
+        <v>2000169796</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>SHANI RANJAN TIWARI</t>
+          <t>KAGITHALA  LOKESH REDDY</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>9-Jan-26</t>
+          <t>18-Oct-25</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>19-Jan-26</t>
+          <t>24-Oct-25</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -3019,17 +3019,17 @@
         </is>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>5.76</v>
+        <v>10.69</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
@@ -3039,42 +3039,42 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>shani.tiwari@deptagency.com</t>
+          <t>kagithala.reddy@deptagency.com</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>Barbour</t>
+          <t>Hubo</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>Sebastian Farao</t>
+          <t>Jasna Tanevska</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>Salesforce CC B2C Developer</t>
+          <t>Shopify Developer</t>
         </is>
       </c>
       <c r="X22" s="6" t="inlineStr">
@@ -3098,20 +3098,20 @@
     <row r="23" ht="34.8" customHeight="1" s="5">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>G4959</t>
+          <t>G6213</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>2000185148</v>
+        <v>2000185667</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>ROMIT  PANDITA</t>
+          <t>SHUBHAM GULAB CHOPADEKAR</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>25-Feb-26</t>
+          <t>20-Mar-26</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>2-Mar-26</t>
+          <t>26-Mar-26</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>12.33</v>
+        <v>5.17</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>romit.pandita@deptagency.com</t>
+          <t>shubham.chopdekar@deptagency.com</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>Arcadis</t>
+          <t>ParsonKelloggs</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
-          <t>Kristen Loch</t>
+          <t>Kaera Hanlon</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>Senior Content Migration Specialist</t>
+          <t>Junior Content Migration Specialist</t>
         </is>
       </c>
       <c r="X23" s="6" t="inlineStr">
         <is>
-          <t>Standard Senior</t>
+          <t>Standard Mid</t>
         </is>
       </c>
       <c r="Y23" s="6" t="inlineStr">
@@ -3224,15 +3224,15 @@
     <row r="24" ht="34.8" customHeight="1" s="5">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>F9294</t>
+          <t>G1139</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>2000169796</v>
+        <v>2000176184</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>KAGITHALA  LOKESH REDDY</t>
+          <t>MUKESH KUMAR SAH</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>18-Oct-25</t>
+          <t>27-Nov-25</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>24-Oct-25</t>
+          <t>1-Dec-25</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -3271,17 +3271,17 @@
         </is>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>10.69</v>
+        <v>13.58</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Drupal</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>kagithala.reddy@deptagency.com</t>
+          <t>mukesh.sah@deptagency.com</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -3306,32 +3306,32 @@
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>UKI</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>Hubo</t>
+          <t>Quintainliving, Glen Dimplex</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>Jasna Tanevska</t>
+          <t>Quintainliving - Simon Molnแr., Glen Dimplex - Pascaline Aries</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Drupal</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>Shopify Developer</t>
+          <t>Drupal Developer</t>
         </is>
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>Premium Senior</t>
+          <t>Premium Lead</t>
         </is>
       </c>
       <c r="Y24" s="6" t="inlineStr">
@@ -3350,20 +3350,20 @@
     <row r="25" ht="46.05" customHeight="1" s="5">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>G6213</t>
+          <t>G2457</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>2000185667</v>
+        <v>2000179781</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>SHUBHAM GULAB CHOPADEKAR</t>
+          <t>AMAAN ULLAH KHAN AHSANULLAH KHAN</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>20-Mar-26</t>
+          <t>26-Dec-25</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>26-Mar-26</t>
+          <t>5-Jan-26</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -3397,17 +3397,17 @@
         </is>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>5.17</v>
+        <v>7.5</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>Content Migration</t>
+          <t>React JS</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
@@ -3417,47 +3417,47 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>shubham.chopdekar@deptagency.com</t>
+          <t>amaan.khan@deptagency.com</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTDE</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>ParsonKelloggs</t>
+          <t>Tennis-Point</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
-          <t>Kaera Hanlon</t>
+          <t>Olga Jไnichen</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>Content Migration</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>Junior Content Migration Specialist</t>
+          <t>Front end developer - React Senior</t>
         </is>
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>Standard Mid</t>
+          <t>Standard Senior</t>
         </is>
       </c>
       <c r="Y25" s="6" t="inlineStr">
@@ -3476,20 +3476,20 @@
     <row r="26" ht="58.4" customHeight="1" s="5">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>G1139</t>
+          <t>G5137</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>2000176184</v>
+        <v>2000184537</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>MUKESH KUMAR SAH</t>
+          <t>PRIYANKA  SHARMA</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>27-Nov-25</t>
+          <t>28-Feb-26</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>1-Dec-25</t>
+          <t>6-Mar-26</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -3523,17 +3523,17 @@
         </is>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>13.58</v>
+        <v>6.32</v>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Drupal</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>mukesh.sah@deptagency.com</t>
+          <t>priyanka.sharma@deptagency.com</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -3558,32 +3558,32 @@
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>UKI</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>Quintainliving, Glen Dimplex</t>
+          <t>Client TBD</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
         <is>
-          <t>Quintainliving - Simon Molnแr., Glen Dimplex - Pascaline Aries</t>
+          <t>PM TBD</t>
         </is>
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>Drupal</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>Drupal Developer</t>
+          <t>Senior Front-end developer</t>
         </is>
       </c>
       <c r="X26" s="6" t="inlineStr">
         <is>
-          <t>Premium Lead</t>
+          <t>Standard Senior</t>
         </is>
       </c>
       <c r="Y26" s="6" t="inlineStr">
@@ -3602,20 +3602,20 @@
     <row r="27" ht="57.3" customHeight="1" s="5">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>G2457</t>
+          <t>G2782</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>2000179781</v>
+        <v>2000173378</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>AMAAN ULLAH KHAN AHSANULLAH KHAN</t>
+          <t>SANKET BANDU GHODECHOR</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>26-Dec-25</t>
+          <t>5-Jan-26</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>5-Jan-26</t>
+          <t>10-Jan-26</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -3649,32 +3649,32 @@
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>7.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>React JS</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>amaan.khan@deptagency.com</t>
+          <t>sanket.ghodechor@deptagency.com</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>DTDE</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>UKI</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>Tennis-Point</t>
+          <t>HSE</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
-          <t>Olga Jไnichen</t>
+          <t>Kirsty Hilliard, Ana Todorovic</t>
         </is>
       </c>
       <c r="V27" s="6" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>Front end developer - React Senior</t>
+          <t>Senior Front end developer</t>
         </is>
       </c>
       <c r="X27" s="6" t="inlineStr">
@@ -3728,20 +3728,20 @@
     <row r="28" ht="34.8" customHeight="1" s="5">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>G5137</t>
+          <t>G6211</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>2000184537</v>
+        <v>2000181755</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>PRIYANKA  SHARMA</t>
+          <t>AKASH  SHRIVASTAV</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>28-Feb-26</t>
+          <t>20-Mar-26</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>6-Mar-26</t>
+          <t>31-Mar-26</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -3775,17 +3775,17 @@
         </is>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>6.32</v>
+        <v>11.27</v>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Dot net CMS</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>priyanka.sharma@deptagency.com</t>
+          <t>akash.shrivastav@deptagency.com</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
@@ -3815,27 +3815,27 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>Client TBD</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>PM TBD</t>
+          <t>Sarah Buizer</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>Senior Front-end developer</t>
+          <t>Backend Developer (.Net+CMS Umbarco)</t>
         </is>
       </c>
       <c r="X28" s="6" t="inlineStr">
         <is>
-          <t>Standard Senior</t>
+          <t>Premium Senior</t>
         </is>
       </c>
       <c r="Y28" s="6" t="inlineStr">
@@ -3854,20 +3854,20 @@
     <row r="29" ht="46.05" customHeight="1" s="5">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>G2782</t>
+          <t>G2406</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>2000173378</v>
+        <v>2000171117</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>SANKET BANDU GHODECHOR</t>
+          <t>HAZARATH  UMAR P</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>5-Jan-26</t>
+          <t>23-Dec-25</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>10-Jan-26</t>
+          <t>2-Jan-26</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -3901,67 +3901,67 @@
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>sanket.ghodechor@deptagency.com</t>
+          <t>hazarath.p@deptagency.com</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>UKI</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>HSE</t>
+          <t>ParsonKelloggs</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>Kirsty Hilliard, Ana Todorovic</t>
+          <t>Federico Flores , Keara Hanlon</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>Senior Front end developer</t>
+          <t>Manual QA Tester</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
         <is>
-          <t>Standard Senior</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y29" s="6" t="inlineStr">
@@ -3980,20 +3980,20 @@
     <row r="30" ht="46.05" customHeight="1" s="5">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>G6211</t>
+          <t>G1888</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>2000181755</v>
+        <v>2000178248</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>AKASH  SHRIVASTAV</t>
+          <t>KARTIK  DHIWAR</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>20-Mar-26</t>
+          <t>13-Dec-25</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>31-Mar-26</t>
+          <t>6-Jan-26</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -4027,17 +4027,17 @@
         </is>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>11.27</v>
+        <v>8.93</v>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>Dot net CMS</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>akash.shrivastav@deptagency.com</t>
+          <t>kartik.dhiwar@deptagency.com</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -4067,27 +4067,27 @@
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>ORTEC</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>Sarah Buizer</t>
+          <t>Tobias Pors</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>Backend Developer (.Net+CMS Umbarco)</t>
+          <t>Manual QA Tester</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>Premium Senior</t>
+          <t>Standard Senior</t>
         </is>
       </c>
       <c r="Y30" s="6" t="inlineStr">
@@ -4104,17 +4104,15 @@
       </c>
     </row>
     <row r="31" ht="34.8" customHeight="1" s="5">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>G2406</t>
-        </is>
+      <c r="A31" s="6" t="n">
+        <v>67277</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>2000171117</v>
+        <v>1000067277</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>HAZARATH  UMAR P</t>
+          <t>PIYUSH VIVEKKUMAR MODY</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4139,12 +4137,12 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>23-Dec-25</t>
+          <t>6-Dec-21</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>2-Jan-26</t>
+          <t>16-Feb-26</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -4153,13 +4151,13 @@
         </is>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.51</v>
+        <v>4.56</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>8.51</v>
+        <v>4.56</v>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -4173,7 +4171,7 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>hazarath.p@deptagency.com</t>
+          <t>piyush.mody@deptagency.com</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
@@ -4193,12 +4191,12 @@
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>ParsonKelloggs</t>
+          <t>CFL</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
         <is>
-          <t>Federico Flores , Keara Hanlon</t>
+          <t>Tom Longo, Daniel Schaerer</t>
         </is>
       </c>
       <c r="V31" s="6" t="inlineStr">
@@ -4213,7 +4211,7 @@
       </c>
       <c r="X31" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Standard Senior</t>
         </is>
       </c>
       <c r="Y31" s="6" t="inlineStr">
@@ -4232,15 +4230,15 @@
     <row r="32" ht="34.8" customHeight="1" s="5">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>G1888</t>
+          <t>F9125</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>2000178248</v>
+        <v>2000171016</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>KARTIK  DHIWAR</t>
+          <t>LODAGALA  SURESH</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -4265,12 +4263,12 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>13-Dec-25</t>
+          <t>14-Oct-25</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>6-Jan-26</t>
+          <t>10-Nov-25</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -4279,13 +4277,13 @@
         </is>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>8.93</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
@@ -4299,32 +4297,32 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>kartik.dhiwar@deptagency.com</t>
+          <t>lodagala.suresh@deptagency.com</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>ORTEC</t>
+          <t>Frette S.R.L., ParsonKelloggs, SBM Life Science Corporation</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>Tobias Pors</t>
+          <t>"Frette-Daniel Huerta, ParsonKelloggs-Keara Hanlon, SBM Life Science Corporation - Sebastian Toledo Farao"</t>
         </is>
       </c>
       <c r="V32" s="6" t="inlineStr">
@@ -4339,7 +4337,7 @@
       </c>
       <c r="X32" s="6" t="inlineStr">
         <is>
-          <t>Standard Senior</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y32" s="6" t="inlineStr">
@@ -4356,20 +4354,22 @@
       </c>
     </row>
     <row r="33" ht="34.8" customHeight="1" s="5">
-      <c r="A33" s="6" t="n">
-        <v>67277</v>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>G0802</t>
+        </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>1000067277</v>
+        <v>2000173027</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>PIYUSH VIVEKKUMAR MODY</t>
+          <t>SURAJ CHHATRAPATI KAVADE</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>6-Dec-21</t>
+          <t>21-Nov-25</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>16-Feb-26</t>
+          <t>26-Nov-25</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -4403,17 +4403,17 @@
         </is>
       </c>
       <c r="K33" s="7" t="n">
-        <v>4.56</v>
+        <v>0.59</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>4.56</v>
+        <v>10.59</v>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -4423,47 +4423,47 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>piyush.mody@deptagency.com</t>
+          <t>suraj.kavade@deptagency.com</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>CFL</t>
+          <t>Managed Services</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
-          <t>Tom Longo, Daniel Schaerer</t>
+          <t>Jasna Tanevska &amp; Mandy Deegeling - Bleekman</t>
         </is>
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>Manual QA Tester</t>
+          <t>Senior Front end developer</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
         <is>
-          <t>Standard Senior</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y33" s="6" t="inlineStr">
@@ -4482,20 +4482,20 @@
     <row r="34" ht="102.2" customHeight="1" s="5">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>F9125</t>
+          <t>G1494</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>2000171016</v>
+        <v>2000176973</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>LODAGALA  SURESH</t>
+          <t>ABHISHEK HITENDRABHAI MODI</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>14-Oct-25</t>
+          <t>5-Dec-25</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>10-Nov-25</t>
+          <t>11-Dec-25</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -4529,17 +4529,17 @@
         </is>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>8.300000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -4549,47 +4549,47 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>lodagala.suresh@deptagency.com</t>
+          <t>abhishek.modi@deptagency.com</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>Frette S.R.L., ParsonKelloggs, SBM Life Science Corporation</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>"Frette-Daniel Huerta, ParsonKelloggs-Keara Hanlon, SBM Life Science Corporation - Sebastian Toledo Farao"</t>
+          <t>Joost Eerbeek</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>Manual QA Tester</t>
+          <t>Front end developer</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Standard Mid</t>
         </is>
       </c>
       <c r="Y34" s="6" t="inlineStr">
@@ -4608,15 +4608,15 @@
     <row r="35" ht="57.3" customHeight="1" s="5">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>G0802</t>
+          <t>F8483</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>2000173027</v>
+        <v>2000158924</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>SURAJ CHHATRAPATI KAVADE</t>
+          <t>AMIT KUMAR SINGH</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>PUNE 3</t>
+          <t>MUMBAIMBP</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>21-Nov-25</t>
+          <t>29-Sep-25</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>26-Nov-25</t>
+          <t>15-Dec-25</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -4655,62 +4655,62 @@
         </is>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>10.59</v>
+        <v>13.74</v>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
+          <t>React JS</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>amitsingh@deptagency.com</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>DTDE</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>DACH</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>Shreya reichelt</t>
+        </is>
+      </c>
+      <c r="V35" s="6" t="inlineStr">
+        <is>
           <t>Front End</t>
         </is>
       </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>suraj.kavade@deptagency.com</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>DTNL</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>BENO</t>
-        </is>
-      </c>
-      <c r="T35" s="6" t="inlineStr">
-        <is>
-          <t>Managed Services</t>
-        </is>
-      </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>Jasna Tanevska &amp; Mandy Deegeling - Bleekman</t>
-        </is>
-      </c>
-      <c r="V35" s="6" t="inlineStr">
-        <is>
-          <t>Front End</t>
-        </is>
-      </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>Senior Front end developer</t>
+          <t>Front end developer - React Senior</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="Y35" s="6" t="inlineStr">
         <is>
-          <t>GCC</t>
+          <t>Non GCC</t>
         </is>
       </c>
       <c r="Z35" s="9" t="n"/>
@@ -4734,20 +4734,20 @@
     <row r="36" ht="34.8" customHeight="1" s="5">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>G1494</t>
+          <t>F8792</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>2000176973</v>
+        <v>2000169148</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>ABHISHEK HITENDRABHAI MODI</t>
+          <t>ANCHAL KUMARI  SINGH</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>5-Dec-25</t>
+          <t>6-Oct-25</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>11-Dec-25</t>
+          <t>8-Oct-25</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -4781,17 +4781,17 @@
         </is>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>10.56</v>
+        <v>6.32</v>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr">
@@ -4801,47 +4801,47 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>abhishek.modi@deptagency.com</t>
+          <t>anchal.singh@deptagency.com</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S36" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Client TBD</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>Joost Eerbeek</t>
+          <t>PM TBD</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
-          <t>Front end developer</t>
+          <t>BE Salesforce Commerce cloud Developer</t>
         </is>
       </c>
       <c r="X36" s="6" t="inlineStr">
         <is>
-          <t>Standard Mid</t>
+          <t>Seniority TBD</t>
         </is>
       </c>
       <c r="Y36" s="6" t="inlineStr">
@@ -4849,26 +4849,34 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z36" s="9" t="n"/>
-      <c r="AA36" s="9" t="n"/>
+      <c r="Z36" s="8" t="inlineStr">
+        <is>
+          <t>24-Apr-26</t>
+        </is>
+      </c>
+      <c r="AA36" s="6" t="inlineStr">
+        <is>
+          <t>Voluntary</t>
+        </is>
+      </c>
       <c r="AB36" s="6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="37" ht="34.8" customHeight="1" s="5">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>F8483</t>
+          <t>F6620</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>2000158924</v>
+        <v>2000164022</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>AMIT KUMAR SINGH</t>
+          <t>SAISH PRADEEP CHACHAD</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -4893,12 +4901,12 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>29-Sep-25</t>
+          <t>23-Aug-25</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>15-Dec-25</t>
+          <t>1-Sep-25</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -4907,17 +4915,17 @@
         </is>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="L37" s="7" t="n">
         <v>13</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>13.74</v>
+        <v>13.84</v>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>React JS</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
@@ -4927,12 +4935,12 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>amitsingh@deptagency.com</t>
+          <t>saish.chachad@deptagency.com</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>DTDE</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -4942,37 +4950,37 @@
       </c>
       <c r="S37" s="6" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Blackroll</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
         <is>
-          <t>Shreya reichelt</t>
+          <t>Job Lampe</t>
         </is>
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>Front end developer - React Senior</t>
+          <t>Mobile iOS developer</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Premium Lead</t>
         </is>
       </c>
       <c r="Y37" s="6" t="inlineStr">
         <is>
-          <t>Non GCC</t>
+          <t>GCC</t>
         </is>
       </c>
       <c r="Z37" s="9" t="n"/>
@@ -4986,20 +4994,20 @@
     <row r="38" ht="46.05" customHeight="1" s="5">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>F8792</t>
+          <t>G1546</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>2000169148</v>
+        <v>2000170541</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>ANCHAL KUMARI  SINGH</t>
+          <t>WASIL AHMAD  SAYYED SABIR ALI</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -5019,12 +5027,12 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>6-Oct-25</t>
+          <t>8-Dec-25</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>8-Oct-25</t>
+          <t>10-Dec-25</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -5033,13 +5041,13 @@
         </is>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>6.32</v>
+        <v>10.55</v>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
@@ -5053,32 +5061,32 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>anchal.singh@deptagency.com</t>
+          <t>wasil.ahmad@deptagency.com</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>Client TBD</t>
+          <t>KETER (Home &amp; Garden Products)</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>PM TBD</t>
+          <t>Folkert Wieringa</t>
         </is>
       </c>
       <c r="V38" s="6" t="inlineStr">
@@ -5088,12 +5096,12 @@
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>BE Salesforce Commerce cloud Developer</t>
+          <t>FE Salesforce Commerce cloud Developer</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
         <is>
-          <t>Seniority TBD</t>
+          <t>Premium Lead</t>
         </is>
       </c>
       <c r="Y38" s="6" t="inlineStr">
@@ -5101,34 +5109,26 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z38" s="8" t="inlineStr">
-        <is>
-          <t>24-Apr-26</t>
-        </is>
-      </c>
-      <c r="AA38" s="6" t="inlineStr">
-        <is>
-          <t>Voluntary</t>
-        </is>
-      </c>
+      <c r="Z38" s="9" t="n"/>
+      <c r="AA38" s="9" t="n"/>
       <c r="AB38" s="6" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34.8" customHeight="1" s="5">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>F6620</t>
+          <t>F9966</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>2000164022</v>
+        <v>2000173029</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>SAISH PRADEEP CHACHAD</t>
+          <t>SIRAJ SIKANDAR PATHAN</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>MUMBAIMBP</t>
+          <t>PUNE 3</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>23-Aug-25</t>
+          <t>3-Nov-25</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>1-Sep-25</t>
+          <t>10-Nov-25</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -5167,17 +5167,17 @@
         </is>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="L39" s="7" t="n">
         <v>13</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>13.84</v>
+        <v>13.64</v>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>saish.chachad@deptagency.com</t>
+          <t>siraj.pathan@deptagency.com</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -5207,27 +5207,27 @@
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
-          <t>Blackroll</t>
+          <t>Client TBD</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
         <is>
-          <t>Job Lampe</t>
+          <t>PM TBD</t>
         </is>
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>Mobile iOS developer</t>
+          <t>Senior Front end developer</t>
         </is>
       </c>
       <c r="X39" s="6" t="inlineStr">
         <is>
-          <t>Premium Lead</t>
+          <t>Seniority TBD</t>
         </is>
       </c>
       <c r="Y39" s="6" t="inlineStr">
@@ -5235,31 +5235,39 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z39" s="9" t="n"/>
-      <c r="AA39" s="9" t="n"/>
+      <c r="Z39" s="8" t="inlineStr">
+        <is>
+          <t>30-Apr-26</t>
+        </is>
+      </c>
+      <c r="AA39" s="6" t="inlineStr">
+        <is>
+          <t>Involuntary</t>
+        </is>
+      </c>
       <c r="AB39" s="6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="40" ht="46.05" customHeight="1" s="5">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>G1546</t>
+          <t>G3864</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>2000170541</v>
+        <v>2000172791</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>WASIL AHMAD  SAYYED SABIR ALI</t>
+          <t>AMAN  JAISWAL</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -5279,12 +5287,12 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>8-Dec-25</t>
+          <t>29-Jan-26</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>10-Dec-25</t>
+          <t>5-Feb-26</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -5293,13 +5301,13 @@
         </is>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M40" s="7" t="n">
-        <v>10.55</v>
+        <v>8.41</v>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
@@ -5313,12 +5321,12 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>wasil.ahmad@deptagency.com</t>
+          <t>aman.jaiswal@deptagency.com</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -5333,12 +5341,12 @@
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>KETER (Home &amp; Garden Products)</t>
+          <t>Audley Travel</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
         <is>
-          <t>Folkert Wieringa</t>
+          <t>Dusica Djisalov</t>
         </is>
       </c>
       <c r="V40" s="6" t="inlineStr">
@@ -5348,12 +5356,12 @@
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>FE Salesforce Commerce cloud Developer</t>
+          <t>Salesforce Core Developer</t>
         </is>
       </c>
       <c r="X40" s="6" t="inlineStr">
         <is>
-          <t>Premium Lead</t>
+          <t>Seniority TBD</t>
         </is>
       </c>
       <c r="Y40" s="6" t="inlineStr">
@@ -5361,31 +5369,39 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z40" s="9" t="n"/>
-      <c r="AA40" s="9" t="n"/>
+      <c r="Z40" s="8" t="inlineStr">
+        <is>
+          <t>15-Jun-26</t>
+        </is>
+      </c>
+      <c r="AA40" s="6" t="inlineStr">
+        <is>
+          <t>Involuntary</t>
+        </is>
+      </c>
       <c r="AB40" s="6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34.8" customHeight="1" s="5">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>F9966</t>
+          <t>G6068</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>2000173029</v>
+        <v>2000188083</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>SIRAJ SIKANDAR PATHAN</t>
+          <t>NIKITA HEMANT  SANKPAL</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -5405,12 +5421,12 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>3-Nov-25</t>
+          <t>17-Mar-26</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>10-Nov-25</t>
+          <t>24-Mar-26</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -5419,27 +5435,27 @@
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>13.64</v>
+        <v>7.78</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>siraj.pathan@deptagency.com</t>
+          <t>nikita.sankpal@deptagency.com</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
@@ -5469,12 +5485,12 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>Senior Front end developer</t>
+          <t>Salesforce Core Developer</t>
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr">
@@ -5489,12 +5505,12 @@
       </c>
       <c r="Z41" s="8" t="inlineStr">
         <is>
-          <t>30-Apr-26</t>
+          <t>24-Apr-26</t>
         </is>
       </c>
       <c r="AA41" s="6" t="inlineStr">
         <is>
-          <t>Involuntary</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="AB41" s="6" t="inlineStr">
@@ -5506,15 +5522,15 @@
     <row r="42" ht="34.8" customHeight="1" s="5">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>G3864</t>
+          <t>G1962</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>2000172791</v>
+        <v>2000177217</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>AMAN  JAISWAL</t>
+          <t>DHEERAJ  KUMAR</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -5539,12 +5555,12 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>29-Jan-26</t>
+          <t>26-Mar-26</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>5-Feb-26</t>
+          <t>20-Apr-26</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -5553,67 +5569,63 @@
         </is>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>8</v>
+        <v>7.11</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>8.41</v>
+        <v>7.36</v>
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="O42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>MuleSoft</t>
+        </is>
+      </c>
+      <c r="O42" s="9" t="n"/>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>aman.jaiswal@deptagency.com</t>
+          <t>dheeraj.kumar@deptagency.com</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="S42" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>Audley Travel</t>
+          <t>ParsonKelloggs, Barbour</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
-          <t>Dusica Djisalov</t>
+          <t>"ParsonKelloggs - Federico Flores Barbour - Sebastian Toledo Farao"</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MuleSoft</t>
         </is>
       </c>
       <c r="W42" s="6" t="inlineStr">
         <is>
-          <t>Salesforce Core Developer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="X42" s="6" t="inlineStr">
         <is>
-          <t>Seniority TBD</t>
+          <t>Standard Senior</t>
         </is>
       </c>
       <c r="Y42" s="6" t="inlineStr">
@@ -5621,34 +5633,26 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z42" s="8" t="inlineStr">
-        <is>
-          <t>15-Jun-26</t>
-        </is>
-      </c>
-      <c r="AA42" s="6" t="inlineStr">
-        <is>
-          <t>Involuntary</t>
-        </is>
-      </c>
+      <c r="Z42" s="9" t="n"/>
+      <c r="AA42" s="9" t="n"/>
       <c r="AB42" s="6" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34.8" customHeight="1" s="5">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>G6068</t>
+          <t>E3115</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>2000188083</v>
+        <v>2000138967</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>NIKITA HEMANT  SANKPAL</t>
+          <t>NATASHA  MOHAPATRA</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -5663,7 +5667,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>PUNE 3</t>
+          <t>BANGALORE</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -5673,12 +5677,12 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>17-Mar-26</t>
+          <t>8-Aug-25</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>8-Aug-25</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -5687,32 +5691,28 @@
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.28</v>
+        <v>0.88</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>7.78</v>
+        <v>7.88</v>
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="O43" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
+          <t>Front End</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="n"/>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>nikita.sankpal@deptagency.com</t>
+          <t>natasha.mohapatra@deptagency.com</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>DTDE</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -5722,32 +5722,32 @@
       </c>
       <c r="S43" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="T43" s="6" t="inlineStr">
         <is>
-          <t>Client TBD</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
         <is>
-          <t>PM TBD</t>
+          <t>Shreya reichelt</t>
         </is>
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W43" s="6" t="inlineStr">
         <is>
-          <t>Salesforce Core Developer</t>
+          <t>Senior Front end developer</t>
         </is>
       </c>
       <c r="X43" s="6" t="inlineStr">
         <is>
-          <t>Seniority TBD</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y43" s="6" t="inlineStr">
@@ -5755,34 +5755,26 @@
           <t>GCC</t>
         </is>
       </c>
-      <c r="Z43" s="8" t="inlineStr">
-        <is>
-          <t>24-Apr-26</t>
-        </is>
-      </c>
-      <c r="AA43" s="6" t="inlineStr">
-        <is>
-          <t>Voluntary</t>
-        </is>
-      </c>
+      <c r="Z43" s="9" t="n"/>
+      <c r="AA43" s="9" t="n"/>
       <c r="AB43" s="6" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="44" ht="57.3" customHeight="1" s="5">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>G1962</t>
+          <t>F7048</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>2000177217</v>
+        <v>2000165444</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>DHEERAJ  KUMAR</t>
+          <t>BATTARU CHETTY  PAVANI</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -5797,7 +5789,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>PUNE 3</t>
+          <t>BANGALORE</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -5807,12 +5799,12 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>26-Mar-26</t>
+          <t>29-Aug-25</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>20-Apr-26</t>
+          <t>1-Sep-25</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -5821,63 +5813,63 @@
         </is>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>7.11</v>
+        <v>11</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>7.36</v>
+        <v>11.82</v>
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>MuleSoft</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="O44" s="9" t="n"/>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>dheeraj.kumar@deptagency.com</t>
+          <t>battaru.pavani@deptagency.com</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>DTNL</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="S44" s="6" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>ParsonKelloggs, Barbour</t>
+          <t>Managed Services, Macarthurglen</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
         <is>
-          <t>"ParsonKelloggs - Federico Flores Barbour - Sebastian Toledo Farao"</t>
+          <t>"Managed Services and Macarthurglen - Jasna Tanevska "</t>
         </is>
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>MuleSoft</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="W44" s="6" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="X44" s="6" t="inlineStr">
         <is>
-          <t>Standard Senior</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y44" s="6" t="inlineStr">
@@ -5896,20 +5888,20 @@
     <row r="45" ht="34.8" customHeight="1" s="5">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>E3115</t>
+          <t>G8126</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>2000138967</v>
+        <v>2000193334</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>NATASHA  MOHAPATRA</t>
+          <t>PRASHANT RAMCHANDRA  BAKLE</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>Grade TBD</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -5919,7 +5911,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>BANGALORE</t>
+          <t>PUNE 3</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -5929,12 +5921,12 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>8-Aug-25</t>
+          <t>25-Apr-26</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>8-Aug-25</t>
+          <t>6-May-26</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -5943,28 +5935,28 @@
         </is>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.88</v>
+        <v>0.17</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>7.88</v>
+        <v>13.17</v>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Business Analysis</t>
         </is>
       </c>
       <c r="O45" s="9" t="n"/>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>natasha.mohapatra@deptagency.com</t>
+          <t>prashant.bakle@deptagency.com</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>DTDE</t>
+          <t>DTIE</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -5974,32 +5966,32 @@
       </c>
       <c r="S45" s="6" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>UKI</t>
         </is>
       </c>
       <c r="T45" s="6" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Audley Travel</t>
         </is>
       </c>
       <c r="U45" s="6" t="inlineStr">
         <is>
-          <t>Shreya reichelt</t>
+          <t>Dusica Djisalov</t>
         </is>
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>Front End</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="W45" s="6" t="inlineStr">
         <is>
-          <t>Senior Front end developer</t>
+          <t>Salesforce Business Analyst</t>
         </is>
       </c>
       <c r="X45" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Premium Lead</t>
         </is>
       </c>
       <c r="Y45" s="6" t="inlineStr">
@@ -6018,15 +6010,15 @@
     <row r="46" ht="57.3" customHeight="1" s="5">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>F7048</t>
+          <t>G8813</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>2000165444</v>
+        <v>2000185852</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>BATTARU CHETTY  PAVANI</t>
+          <t>SHIVAM  SONI</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -6041,7 +6033,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>BANGALORE</t>
+          <t>PUNE 3</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -6051,12 +6043,12 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>29-Aug-25</t>
+          <t>11-May-26</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>1-Sep-25</t>
+          <t>22-May-26</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -6065,23 +6057,23 @@
         </is>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.82</v>
+        <v>0.13</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>11.82</v>
+        <v>0.13</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Dot net CMS</t>
         </is>
       </c>
       <c r="O46" s="9" t="n"/>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>battaru.pavani@deptagency.com</t>
+          <t>shivam.soni@deptagency.com</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
@@ -6101,27 +6093,27 @@
       </c>
       <c r="T46" s="6" t="inlineStr">
         <is>
-          <t>Managed Services, Macarthurglen</t>
+          <t>Client TBD</t>
         </is>
       </c>
       <c r="U46" s="6" t="inlineStr">
         <is>
-          <t>"Managed Services and Macarthurglen - Jasna Tanevska "</t>
+          <t>PM TBD</t>
         </is>
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="W46" s="6" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>.Net+CMS Senior Developer</t>
         </is>
       </c>
       <c r="X46" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Premium Senior</t>
         </is>
       </c>
       <c r="Y46" s="6" t="inlineStr">
@@ -6140,20 +6132,20 @@
     <row r="47" ht="34.8" customHeight="1" s="5">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>G8126</t>
+          <t>G9444</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>2000193334</v>
+        <v>2000190465</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>PRASHANT RAMCHANDRA  BAKLE</t>
+          <t>ASHOK BRIJLAL RAJANI</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Grade TBD</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -6173,12 +6165,12 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>25-Apr-26</t>
+          <t>21-May-26</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>6-May-26</t>
+          <t>27-May-26</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -6187,28 +6179,28 @@
         </is>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>13.17</v>
+        <v>28.1</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>Business Analysis</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="O47" s="9" t="n"/>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>prashant.bakle@deptagency.com</t>
+          <t>ashok.rajani@deptagency.com</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>DTIE</t>
+          <t>DTUK</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -6228,7 +6220,7 @@
       </c>
       <c r="U47" s="6" t="inlineStr">
         <is>
-          <t>Dusica Djisalov</t>
+          <t>Laura Archer</t>
         </is>
       </c>
       <c r="V47" s="6" t="inlineStr">
@@ -6238,12 +6230,12 @@
       </c>
       <c r="W47" s="6" t="inlineStr">
         <is>
-          <t>Salesforce Business Analyst</t>
+          <t>Salesforce Technical Service Delivery Manager</t>
         </is>
       </c>
       <c r="X47" s="6" t="inlineStr">
         <is>
-          <t>Premium Lead</t>
+          <t>Premium Technical Service Delivery Manager</t>
         </is>
       </c>
       <c r="Y47" s="6" t="inlineStr">
@@ -6262,15 +6254,15 @@
     <row r="48" ht="34.8" customHeight="1" s="5">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>G8813</t>
+          <t>G9834</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>2000185852</v>
+        <v>2000197076</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>SHIVAM  SONI</t>
+          <t>SHWETA SAURABH SRIVASTAV</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -6295,12 +6287,12 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>11-May-26</t>
+          <t>27-May-26</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>22-May-26</t>
+          <t>3-Jun-26</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -6309,13 +6301,13 @@
         </is>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="L48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
@@ -6325,12 +6317,12 @@
       <c r="O48" s="9" t="n"/>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>shivam.soni@deptagency.com</t>
+          <t>shweta.srivastav@deptagency.com</t>
         </is>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>DTNL</t>
+          <t>DTUK</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -6340,17 +6332,17 @@
       </c>
       <c r="S48" s="6" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>UKI</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
         <is>
-          <t>Client TBD</t>
+          <t>INEOS-Automotive</t>
         </is>
       </c>
       <c r="U48" s="6" t="inlineStr">
         <is>
-          <t>PM TBD</t>
+          <t>Colin Kelly</t>
         </is>
       </c>
       <c r="V48" s="6" t="inlineStr">
@@ -6360,12 +6352,12 @@
       </c>
       <c r="W48" s="6" t="inlineStr">
         <is>
-          <t>.Net+CMS Senior Developer</t>
+          <t>Principal .Net+ CMS Developer</t>
         </is>
       </c>
       <c r="X48" s="6" t="inlineStr">
         <is>
-          <t>Premium Senior</t>
+          <t>Premium Mid</t>
         </is>
       </c>
       <c r="Y48" s="6" t="inlineStr">
@@ -6384,20 +6376,20 @@
     <row r="49" ht="57.3" customHeight="1" s="5">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>G9444</t>
+          <t>G0359</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>2000190465</v>
+        <v>2000173958</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>ASHOK BRIJLAL RAJANI</t>
+          <t>Ashvin Patel</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -6407,7 +6399,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>PUNE 3</t>
+          <t>BANGALORE</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -6417,12 +6409,12 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>21-May-26</t>
+          <t>11-Nov-25</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>27-May-26</t>
+          <t>16-Jun-26</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
@@ -6431,68 +6423,64 @@
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>28.1</v>
+        <v>0.62</v>
       </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Java + AWS</t>
         </is>
       </c>
       <c r="O49" s="9" t="n"/>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>ashok.rajani@deptagency.com</t>
-        </is>
-      </c>
+      <c r="P49" s="9" t="n"/>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>DTUK</t>
+          <t>DTAU</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>APAC</t>
         </is>
       </c>
       <c r="S49" s="6" t="inlineStr">
         <is>
-          <t>UKI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="T49" s="6" t="inlineStr">
         <is>
-          <t>Audley Travel</t>
+          <t>Livewire project</t>
         </is>
       </c>
       <c r="U49" s="6" t="inlineStr">
         <is>
-          <t>Laura Archer</t>
+          <t>Ben Loft</t>
         </is>
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="W49" s="6" t="inlineStr">
         <is>
-          <t>Salesforce Technical Service Delivery Manager</t>
+          <t>AWS Backend Lead Developer</t>
         </is>
       </c>
       <c r="X49" s="6" t="inlineStr">
         <is>
-          <t>Premium Technical Service Delivery Manager</t>
+          <t>Standard Lead</t>
         </is>
       </c>
       <c r="Y49" s="6" t="inlineStr">
         <is>
-          <t>GCC</t>
+          <t>Non GCC</t>
         </is>
       </c>
       <c r="Z49" s="9" t="n"/>
@@ -6506,15 +6494,15 @@
     <row r="50" ht="34.8" customHeight="1" s="5">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>G9834</t>
+          <t>G9036</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>2000197076</v>
+        <v>2000194634</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>SHWETA SAURABH SRIVASTAV</t>
+          <t>Rahul Malhotra</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -6539,12 +6527,12 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>27-May-26</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>3-Jun-26</t>
+          <t>14-May-26</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -6553,63 +6541,59 @@
         </is>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="L50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>Dot net CMS</t>
+          <t>Vue JS</t>
         </is>
       </c>
       <c r="O50" s="9" t="n"/>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>shweta.srivastav@deptagency.com</t>
-        </is>
-      </c>
+      <c r="P50" s="9" t="n"/>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>DTUK</t>
+          <t>Entity TBD</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Region TBD</t>
         </is>
       </c>
       <c r="S50" s="6" t="inlineStr">
         <is>
-          <t>UKI</t>
+          <t>Market TBD</t>
         </is>
       </c>
       <c r="T50" s="6" t="inlineStr">
         <is>
-          <t>INEOS-Automotive</t>
+          <t>Client TBD</t>
         </is>
       </c>
       <c r="U50" s="6" t="inlineStr">
         <is>
-          <t>Colin Kelly</t>
+          <t>PM TBD</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>Front End</t>
         </is>
       </c>
       <c r="W50" s="6" t="inlineStr">
         <is>
-          <t>Principal .Net+ CMS Developer</t>
+          <t>Front End Developer Vue JS</t>
         </is>
       </c>
       <c r="X50" s="6" t="inlineStr">
         <is>
-          <t>Premium Mid</t>
+          <t>Seniority TBD</t>
         </is>
       </c>
       <c r="Y50" s="6" t="inlineStr">
@@ -6621,27 +6605,27 @@
       <c r="AA50" s="9" t="n"/>
       <c r="AB50" s="6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Strategic Pool</t>
         </is>
       </c>
     </row>
     <row r="51" ht="34.8" customHeight="1" s="5">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>G0359</t>
+          <t>EMP ID TBD</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>2000173958</v>
+        <v>2000195658</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Ashvin Patel</t>
+          <t>Shorya Sharma</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>Grade TBD</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -6651,7 +6635,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>BANGALORE</t>
+          <t>PUNE 3</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -6661,12 +6645,12 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>11-Nov-25</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>16-Jun-26</t>
+          <t>22-Jun-26</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -6675,310 +6659,76 @@
         </is>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.62</v>
+        <v>0.01</v>
       </c>
       <c r="L51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0.62</v>
+        <v>0.01</v>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>Java + AWS</t>
+          <t>Agentic AI</t>
         </is>
       </c>
       <c r="O51" s="9" t="n"/>
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>DTAU</t>
+          <t>Entity TBD</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>Region TBD</t>
         </is>
       </c>
       <c r="S51" s="6" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Market TBD</t>
         </is>
       </c>
       <c r="T51" s="6" t="inlineStr">
         <is>
-          <t>Livewire project</t>
+          <t>Client TBD</t>
         </is>
       </c>
       <c r="U51" s="6" t="inlineStr">
         <is>
-          <t>Ben Loft</t>
+          <t>PM TBD</t>
         </is>
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Agentic AI</t>
         </is>
       </c>
       <c r="W51" s="6" t="inlineStr">
         <is>
-          <t>AWS Backend Lead Developer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="X51" s="6" t="inlineStr">
         <is>
-          <t>Standard Lead</t>
+          <t>Seniority TBD</t>
         </is>
       </c>
       <c r="Y51" s="6" t="inlineStr">
         <is>
-          <t>Non GCC</t>
+          <t>GCC</t>
         </is>
       </c>
       <c r="Z51" s="9" t="n"/>
       <c r="AA51" s="9" t="n"/>
       <c r="AB51" s="6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Strategic Pool</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="34.8" customHeight="1" s="5">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>G9036</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="n">
-        <v>2000194634</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Rahul Malhotra</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>G5</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>OFFSHORE</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>PUNE 3</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>MILIND  VIJAY MOKASHI</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>14-May-26</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>26-Jun-26</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>Vue JS</t>
-        </is>
-      </c>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>Entity TBD</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>Region TBD</t>
-        </is>
-      </c>
-      <c r="S52" s="6" t="inlineStr">
-        <is>
-          <t>Market TBD</t>
-        </is>
-      </c>
-      <c r="T52" s="6" t="inlineStr">
-        <is>
-          <t>Client TBD</t>
-        </is>
-      </c>
-      <c r="U52" s="6" t="inlineStr">
-        <is>
-          <t>PM TBD</t>
-        </is>
-      </c>
-      <c r="V52" s="6" t="inlineStr">
-        <is>
-          <t>Front End</t>
-        </is>
-      </c>
-      <c r="W52" s="6" t="inlineStr">
-        <is>
-          <t>Front End Developer Vue JS</t>
-        </is>
-      </c>
-      <c r="X52" s="6" t="inlineStr">
-        <is>
-          <t>Seniority TBD</t>
-        </is>
-      </c>
-      <c r="Y52" s="6" t="inlineStr">
-        <is>
-          <t>GCC</t>
-        </is>
-      </c>
-      <c r="Z52" s="9" t="n"/>
-      <c r="AA52" s="9" t="n"/>
-      <c r="AB52" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="34.8" customHeight="1" s="5">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>EMP ID TBD</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="n">
-        <v>2000195658</v>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Shorya Sharma</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Grade TBD</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>OFFSHORE</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>PUNE 3</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>MILIND  VIJAY MOKASHI</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>22-Jun-26</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>26-Jun-26</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>Agentic AI</t>
-        </is>
-      </c>
-      <c r="O53" s="9" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Entity TBD</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>Region TBD</t>
-        </is>
-      </c>
-      <c r="S53" s="6" t="inlineStr">
-        <is>
-          <t>Market TBD</t>
-        </is>
-      </c>
-      <c r="T53" s="6" t="inlineStr">
-        <is>
-          <t>Client TBD</t>
-        </is>
-      </c>
-      <c r="U53" s="6" t="inlineStr">
-        <is>
-          <t>PM TBD</t>
-        </is>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
-        <is>
-          <t>Agentic AI</t>
-        </is>
-      </c>
-      <c r="W53" s="6" t="inlineStr">
-        <is>
-          <t>Gen AI Engineer</t>
-        </is>
-      </c>
-      <c r="X53" s="6" t="inlineStr">
-        <is>
-          <t>Seniority TBD</t>
-        </is>
-      </c>
-      <c r="Y53" s="6" t="inlineStr">
-        <is>
-          <t>GCC</t>
-        </is>
-      </c>
-      <c r="Z53" s="9" t="n"/>
-      <c r="AA53" s="9" t="n"/>
-      <c r="AB53" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
+    <row r="52" ht="34.8" customHeight="1" s="5"/>
+    <row r="53" ht="34.8" customHeight="1" s="5"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/backend/data/DEPT - Master Data(Sheet1).xlsx
+++ b/backend/data/DEPT - Master Data(Sheet1).xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">Market</t>
   </si>
   <si>
-    <t xml:space="preserve">Client as on June 2026</t>
+    <t xml:space="preserve">Client</t>
   </si>
   <si>
     <t xml:space="preserve">Project Manager</t>
@@ -732,6 +732,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Quintainliving - Simon Moln</t>
     </r>
@@ -740,6 +741,7 @@
         <sz val="10"/>
         <rFont val="Tahoma"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">แ</t>
     </r>
@@ -748,6 +750,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">r., Glen Dimplex - Pascaline Aries</t>
     </r>
@@ -773,6 +776,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Olga J</t>
     </r>
@@ -781,6 +785,7 @@
         <sz val="10"/>
         <rFont val="Tahoma"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ไ</t>
     </r>
@@ -789,6 +794,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">nichen</t>
     </r>
@@ -1353,6 +1359,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1373,11 +1380,13 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Tahoma"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1427,23 +1436,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/backend/data/DEPT - Master Data(Sheet1).xlsx
+++ b/backend/data/DEPT - Master Data(Sheet1).xlsx
@@ -11,6 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$AB$53</definedName>
     <definedName function="false" hidden="false" name="DEPT___Master_Data_Sheet1__A1_AB51" vbProcedure="false">Sheet1!$A$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -1465,7 +1466,20 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2076,8 +2090,6 @@
       <c r="Y6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
       <c r="AB6" s="1" t="s">
         <v>72</v>
       </c>
@@ -2732,8 +2744,6 @@
       <c r="Y14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
       <c r="AB14" s="1" t="s">
         <v>72</v>
       </c>
@@ -5889,6 +5899,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AB53"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5896,5 +5907,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>